--- a/ig/DM-37/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
+++ b/ig/DM-37/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -281,6 +281,12 @@
   </si>
   <si>
     <t>Filière endométriose - troisième niveau de recours</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Centre labellisé Covid-Long</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R344-NiveauExpertise/FHIR/TRE-R344-NiveauExpertise</t>
@@ -623,7 +629,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -832,18 +838,26 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>38</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B27" t="s" s="2">
-        <v>89</v>
+      <c r="B28" t="s" s="2">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
